--- a/Part1_input_prep/all_samples_all_data_LQ.xlsx
+++ b/Part1_input_prep/all_samples_all_data_LQ.xlsx
@@ -13950,7 +13950,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>T.ADAPATATIVO</t>
         </is>
       </c>
     </row>
@@ -52951,6 +52951,11 @@
       </c>
       <c r="B1880">
         <v>100</v>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>HOMBRE</t>
+        </is>
       </c>
       <c r="D1880">
         <v>20</v>

--- a/Part1_input_prep/all_samples_all_data_LQ.xlsx
+++ b/Part1_input_prep/all_samples_all_data_LQ.xlsx
@@ -13950,7 +13950,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>T.ADAPATATIVO</t>
+          <t>T.ADAPTATIVO</t>
         </is>
       </c>
     </row>
